--- a/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>NU</t>
   </si>
@@ -656,238 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2404900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2136800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1868600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1618700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1450500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1306900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1157600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>877300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>636000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>480900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>336100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>245100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>202600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>156100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>162300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>669200</v>
+      </c>
+      <c r="E9" s="3">
         <v>594400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>496200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>493000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>457000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>504400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>455500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>307500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>209400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>130000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>87000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>58100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>70600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>55900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>47900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1735700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1542400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1372400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1125700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>993500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>802500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>702100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>569800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>426600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>350900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>249100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>187000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>132000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>100200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>114400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>149800</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -906,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -956,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1056,58 +1075,64 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E15" s="3">
         <v>19200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>14000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>13200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>10400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1845000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1725200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1544700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1375000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1672300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1301800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1182200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>944900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>724500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>502700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>342600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>298400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>228400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>180700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>157400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>559900</v>
+      </c>
+      <c r="E18" s="3">
         <v>411600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>323900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>243700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-221800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-24600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-67600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-88500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-21800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-53300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-25800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,8 +1275,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1282,69 +1315,75 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-88000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>576500</v>
+      </c>
+      <c r="E21" s="3">
         <v>430700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>338000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>256800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-211900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-14200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-60000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-82100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-50900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-110100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-45900</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1393,108 +1432,117 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>559900</v>
+      </c>
+      <c r="E23" s="3">
         <v>411500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>324000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>243600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-221700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-67700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-88500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-53400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-113800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-37800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>199100</v>
+      </c>
+      <c r="E24" s="3">
         <v>108500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>99100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>101900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>75900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-22600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-22200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-6700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>360900</v>
+      </c>
+      <c r="E26" s="3">
         <v>303000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>224900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>141800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-297600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-29900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-45000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-66300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-49500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-107100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>360900</v>
+      </c>
+      <c r="E27" s="3">
         <v>303000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>224900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>141800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-297600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-29700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-45100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-66100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-49500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-107100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,8 +1909,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1882,69 +1951,75 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>88000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>360900</v>
+      </c>
+      <c r="E33" s="3">
         <v>303000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>224900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>141800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-297600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-29700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-45100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-66100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-49500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-107100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>360900</v>
+      </c>
+      <c r="E35" s="3">
         <v>303000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>224900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>141800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-297600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-29700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-45100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-66100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-49500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-107100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,47 +2223,48 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5068500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2662200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5233500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4178700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3959100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1803600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1079100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>905300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>177000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>167600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>185100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>252600</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2188,8 +2274,11 @@
       <c r="R41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2238,40 +2327,43 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1689000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1600700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1346600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1076700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>521700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>381800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>374200</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2288,8 +2380,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2338,47 +2433,50 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>81700</v>
+      </c>
+      <c r="E45" s="3">
         <v>84300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>74000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>73200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>61700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>44900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>59900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>51900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2388,8 +2486,11 @@
       <c r="R45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2438,47 +2539,50 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>33854300</v>
+      </c>
+      <c r="E47" s="3">
         <v>29006400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>24749700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>22297500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>23683700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>22249600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>22212800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>21798200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>18536400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13727100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>12859000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9512800</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2488,47 +2592,50 @@
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E48" s="3">
         <v>62000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>51700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>46900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>37900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>40500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>37200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2538,47 +2645,50 @@
       <c r="R48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>693400</v>
+      </c>
+      <c r="E49" s="3">
         <v>675400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>651900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>612800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>579600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>565300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>557000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>530100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>474200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>455700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>450900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2588,8 +2698,11 @@
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,47 +2804,50 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1768500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1559200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1423600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1134600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>968500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>820000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>710200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>676100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>436900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>392500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>321500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>215000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2738,8 +2857,11 @@
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,47 +2910,50 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43345200</v>
+      </c>
+      <c r="E54" s="3">
         <v>35693200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>33608100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>29489400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29916600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26007000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25188700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24258000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19858700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14926100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13951500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10121100</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>8</v>
       </c>
@@ -2838,8 +2963,11 @@
       <c r="R54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,47 +3007,48 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9755300</v>
+      </c>
+      <c r="E57" s="3">
         <v>7834900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7749600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6871800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7054800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5894400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5931000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5920800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4882200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4127700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3990400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2982500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
@@ -2928,47 +3058,50 @@
       <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23901600</v>
+      </c>
+      <c r="E58" s="3">
         <v>19361500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18221300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15938800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16044100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14131600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13310100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12600100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9670300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8089800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7505700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5497200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
@@ -2978,47 +3111,50 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1467700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1012600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>712200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>360500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>601600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>430900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>308000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>256400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>339100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>234800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>160800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>75900</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3028,8 +3164,11 @@
       <c r="R59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3078,47 +3217,50 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1173300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1031900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>741000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>633500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>567600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>441400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>495900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>168000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>164900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>169900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>117100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>513600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3128,47 +3270,50 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E62" s="3">
         <v>80600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>89700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>67900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>59100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>59600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>60600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>64600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>47400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>97700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>69800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>53700</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3178,8 +3323,11 @@
       <c r="R62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,47 +3482,50 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36938800</v>
+      </c>
+      <c r="E66" s="3">
         <v>29803900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27963500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24280900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25025800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21254300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20450500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19469000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15417600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13022400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12014400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9317200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>8</v>
       </c>
@@ -3378,8 +3535,11 @@
       <c r="R66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,47 +3768,50 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1276900</v>
+      </c>
+      <c r="E72" s="3">
         <v>887800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>546700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>257100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>64600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-45900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-95900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-116800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-128400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-108900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-104800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-117300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
@@ -3648,8 +3821,11 @@
       <c r="R72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,47 +3980,50 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6406400</v>
+      </c>
+      <c r="E76" s="3">
         <v>5889300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5644600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5208500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4890800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4752700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4738200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4789000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4441000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1903700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1937100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>803800</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>8</v>
       </c>
@@ -3848,8 +4033,11 @@
       <c r="R76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>360900</v>
+      </c>
+      <c r="E81" s="3">
         <v>303000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>224900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>141800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-297600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-29700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-45100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-66100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-49500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-107100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,58 +4220,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E83" s="3">
         <v>19200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2706500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3234400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1699800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>94300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>228400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-15400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>464300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>78300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1859100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-796200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-47100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-221900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-191600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>564800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>660700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,58 +4612,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-47500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-52100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-33600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-47500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-52100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-46500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-33600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-27700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-38200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-109300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4663,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,154 +5055,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E100" s="3">
         <v>327200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>68200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>19900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>105300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>324200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>225600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2541200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>61400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>339000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>394400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-24400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>291500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>148700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>70500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>173600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>41800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-28500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>57000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>78600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>279200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-310400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>505500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-388800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-74700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-143000</v>
       </c>
     </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2709800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2961400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1864600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>138200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>479500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>732400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>262900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>709000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-665700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>461800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-143100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>286500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>149800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>874900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-214100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>NU</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2735900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2404900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2136800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1868600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1618700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1450500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1306900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1157600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>877300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>636000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>480900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>336100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>245100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>202600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>156100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>162300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>723700</v>
+      </c>
+      <c r="E9" s="3">
         <v>669200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>594400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>496200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>493000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>457000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>504400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>455500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>307500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>209400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>130000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>87000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>58100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>70600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>55900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>47900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2012200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1735700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1542400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1372400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1125700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>993500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>802500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>702100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>569800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>426600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>350900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>249100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>187000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>132000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>100200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>114400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>149800</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,8 +1042,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1078,61 +1098,67 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E15" s="3">
         <v>16500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2157400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1845000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1725200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1544700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1375000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1672300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1301800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1182200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>944900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>724500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>502700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>342600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>298400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>228400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>180700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>157400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>578500</v>
+      </c>
+      <c r="E18" s="3">
         <v>559900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>411600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>323900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>243700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-221800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-24600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-67600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-88500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-21800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-53300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,8 +1309,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1318,72 +1352,78 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-88000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-13200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>597000</v>
+      </c>
+      <c r="E21" s="3">
         <v>576500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>430700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>338000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>256800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-211900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-60000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-82100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-50900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-110100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-37000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-45900</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1435,114 +1475,123 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>578500</v>
+      </c>
+      <c r="E23" s="3">
         <v>559900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>411500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>324000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>243600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-221700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-67700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-88500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-53400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-113800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-37800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>199700</v>
+      </c>
+      <c r="E24" s="3">
         <v>199100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>108500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>99100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>101900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>75900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-22600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-22200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>378800</v>
+      </c>
+      <c r="E26" s="3">
         <v>360900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>303000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>224900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>141800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-297600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-29900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-45000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-66300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-34400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-49500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-107100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-32600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>378800</v>
+      </c>
+      <c r="E27" s="3">
         <v>360900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>303000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>224900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>141800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-297600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-29700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-45100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-66100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-49500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-107100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-32600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,8 +1979,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1954,72 +2024,78 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>88000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>13200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>378800</v>
+      </c>
+      <c r="E33" s="3">
         <v>360900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>303000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>224900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>141800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-297600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-29700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-45100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-66100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-49500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-107100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-32600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>378800</v>
+      </c>
+      <c r="E35" s="3">
         <v>360900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>303000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>224900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>141800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-297600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-29700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-45100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-66100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-49500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-107100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-32600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,50 +2310,51 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5736900</v>
+      </c>
+      <c r="E41" s="3">
         <v>5068500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2662200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5233500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4178700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3959100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1803600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1079100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>905300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>177000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>167600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>185100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>252600</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2277,8 +2364,11 @@
       <c r="S41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2330,43 +2420,46 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1406000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1689000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1600700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1346600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1076700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>521700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>381800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>374200</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2383,8 +2476,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2436,50 +2532,53 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>148300</v>
+      </c>
+      <c r="E45" s="3">
         <v>81700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>84300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>74000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>73200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>61700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>44900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>59900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>51900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9100</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2489,8 +2588,11 @@
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2542,50 +2644,53 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>33715400</v>
+      </c>
+      <c r="E47" s="3">
         <v>33854300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>29006400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>24749700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>22297500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>23683700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>22249600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>22212800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>21798200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>18536400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13727100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12859000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9512800</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2595,50 +2700,53 @@
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E48" s="3">
         <v>69800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>62000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>51700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>46500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>37900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>40500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17900</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2648,50 +2756,53 @@
       <c r="S48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>705000</v>
+      </c>
+      <c r="E49" s="3">
         <v>693400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>675400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>651900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>612800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>579600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>565300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>557000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>530100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>474200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>455700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>450900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,50 +2924,53 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1955700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1768500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1559200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1423600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1134600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>968500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>820000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>710200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>676100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>436900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>392500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>321500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>215000</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,50 +3036,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43839500</v>
+      </c>
+      <c r="E54" s="3">
         <v>43345200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>35693200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33608100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29489400</v>
       </c>
-      <c r="H54" s="3">
-        <v>29916600</v>
-      </c>
       <c r="I54" s="3">
+        <v>29934900</v>
+      </c>
+      <c r="J54" s="3">
         <v>26007000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25188700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24258000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19858700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14926100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13951500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10121100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>8</v>
       </c>
@@ -2966,8 +3092,11 @@
       <c r="S54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,50 +3138,51 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9572500</v>
+      </c>
+      <c r="E57" s="3">
         <v>9755300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7834900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7749600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6871800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7054800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5894400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5931000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5920800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4882200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4127700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3990400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2982500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3061,50 +3192,53 @@
       <c r="S57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>23901600</v>
+        <v>24981700</v>
       </c>
       <c r="E58" s="3">
+        <v>24015200</v>
+      </c>
+      <c r="F58" s="3">
         <v>19361500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18221300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15938800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16044100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14131600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13310100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12600100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9670300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8089800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7505700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5497200</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3114,50 +3248,53 @@
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>511900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1467700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1012600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>712200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>360500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>601600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>430900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>308000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>256400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>339100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>234800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>160800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>75900</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3167,8 +3304,11 @@
       <c r="S59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3220,50 +3360,53 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1173300</v>
+        <v>1341200</v>
       </c>
       <c r="E61" s="3">
+        <v>1059700</v>
+      </c>
+      <c r="F61" s="3">
         <v>1031900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>741000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>633500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>567600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>441400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>495900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>168000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>164900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>169900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>117100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>513600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3273,50 +3416,53 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E62" s="3">
         <v>8100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>80600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>89700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>67900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>59100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>59600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>60600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>64600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>47400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>97700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>69800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>53700</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,50 +3640,53 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>37036800</v>
+      </c>
+      <c r="E66" s="3">
         <v>36938800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>29803900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>27963500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24280900</v>
       </c>
-      <c r="H66" s="3">
-        <v>25025800</v>
-      </c>
       <c r="I66" s="3">
+        <v>25044100</v>
+      </c>
+      <c r="J66" s="3">
         <v>21254300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20450500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19469000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15417600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13022400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12014400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9317200</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>8</v>
       </c>
@@ -3538,8 +3696,11 @@
       <c r="S66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,50 +3942,53 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1276900</v>
+        <v>1716100</v>
       </c>
       <c r="E72" s="3">
+        <v>2553900</v>
+      </c>
+      <c r="F72" s="3">
         <v>887800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>546700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>257100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>64600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-45900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-95900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-116800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-128400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-108900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-104800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-117300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>8</v>
       </c>
@@ -3824,8 +3998,11 @@
       <c r="S72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,50 +4166,53 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6802700</v>
+      </c>
+      <c r="E76" s="3">
         <v>6406400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5889300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5644600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5208500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4890800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4752700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4738200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4789000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4441000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1903700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1937100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>803800</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4036,8 +4222,11 @@
       <c r="S76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>378800</v>
+      </c>
+      <c r="E81" s="3">
         <v>360900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>303000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>224900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>141800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-297600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-29700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-45100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-66100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-49500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-107100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-32600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,61 +4419,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E83" s="3">
         <v>16500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>19200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-570600</v>
+      </c>
+      <c r="E89" s="3">
         <v>2706500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3234400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1699800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>94300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>228400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-15400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>464300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>78300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1859100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-796200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-47100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-221900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-191600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>564800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>660700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,61 +4833,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-47500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-52100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-46500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-27700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-33600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-38300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-47500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-52100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-46500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-33600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-38200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-109300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,163 +5301,175 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>258200</v>
+      </c>
+      <c r="E100" s="3">
         <v>9900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>327200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>68200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>19900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>105300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>324200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>225600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2541200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>61400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>339000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>394400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-15600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>291500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>449400</v>
+      </c>
+      <c r="E101" s="3">
         <v>24300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>148700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>70500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>173600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>41800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-28500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>57000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>78600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>279200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-310400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>505500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-388800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-74700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-143000</v>
       </c>
     </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>110200</v>
+      </c>
+      <c r="E102" s="3">
         <v>2709800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2961400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1864600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>138200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>479500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>732400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>262900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>709000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-665700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>461800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-143100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>286500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>149800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>874900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-214100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>NU</t>
   </si>
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2848700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2735900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2404900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2136800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1868600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1618700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1450500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1306900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1157600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>877300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>636000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>480900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>336100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>245100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>202600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>156100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>162300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>729500</v>
+      </c>
+      <c r="E9" s="3">
         <v>723700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>669200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>594400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>496200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>493000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>457000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>504400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>455500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>307500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>209400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>130000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>87000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>58100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>70600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>55900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>47900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2119200</v>
+      </c>
+      <c r="E10" s="3">
         <v>2012200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1735700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1542400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1372400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1125700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>993500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>802500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>702100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>569800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>426600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>350900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>249100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>187000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>132000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>100200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>114400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>149800</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,8 +1062,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1101,64 +1121,70 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E15" s="3">
         <v>18500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>10400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>6400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2123300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2157400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1845000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1725200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1544700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1375000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1672300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1301800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1182200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>944900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>724500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>502700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>342600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>298400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>228400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>180700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>157400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>725400</v>
+      </c>
+      <c r="E18" s="3">
         <v>578500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>559900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>411600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>323900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>243700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-221800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-67600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-88500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-53300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-25800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-24600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,8 +1343,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1355,75 +1389,81 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-88000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-13200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>743800</v>
+      </c>
+      <c r="E21" s="3">
         <v>597000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>576500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>430700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>338000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>256800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-211900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-14200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-60000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-82100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-50900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-110100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-37000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-45900</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1478,120 +1518,129 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>725400</v>
+      </c>
+      <c r="E23" s="3">
         <v>578500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>559900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>411500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>324000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>243600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-221700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-67700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-88500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-53400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-113800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-37800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>238100</v>
+      </c>
+      <c r="E24" s="3">
         <v>199700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>199100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>108500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>99100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>101900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>75900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-22600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-22200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-6700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-5300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>487300</v>
+      </c>
+      <c r="E26" s="3">
         <v>378800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>360900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>303000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>224900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>141800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-297600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-29900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-45000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-66300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-34400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-107100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-32600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>487300</v>
+      </c>
+      <c r="E27" s="3">
         <v>378800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>360900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>303000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>224900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>141800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-297600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-45100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-66100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-34200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-107100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-32600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,8 +2049,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2027,75 +2097,81 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>88000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>13200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>487300</v>
+      </c>
+      <c r="E33" s="3">
         <v>378800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>360900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>303000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>224900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>141800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-297600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-45100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-66100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-34200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-107100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-32600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>487300</v>
+      </c>
+      <c r="E35" s="3">
         <v>378800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>360900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>303000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>224900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>141800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-297600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-45100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-66100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-34200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-107100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-32600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,53 +2397,54 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6537000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5736900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5068500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2662200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5233500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4178700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3959100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1803600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1079100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>905300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>177000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>167600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>185100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>252600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2367,8 +2454,11 @@
       <c r="T41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,46 +2513,49 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>954000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1406000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1689000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1600700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1346600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1076700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>521700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>381800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>374200</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2479,8 +2572,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2535,53 +2631,56 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>128600</v>
+      </c>
+      <c r="E45" s="3">
         <v>148300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>81700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>84300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>74000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>73200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>61700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>44900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>59900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>51900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2591,8 +2690,11 @@
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2647,53 +2749,56 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34370900</v>
+      </c>
+      <c r="E47" s="3">
         <v>33715400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>33854300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>29006400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>24749700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>22297500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>23683700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>22249600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>22212800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>21798200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>18536400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13727100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12859000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9512800</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2703,53 +2808,56 @@
       <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E48" s="3">
         <v>65500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>69800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>62000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>51700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>46900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>46500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>37900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>40500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2759,53 +2867,56 @@
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>703600</v>
+      </c>
+      <c r="E49" s="3">
         <v>705000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>693400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>675400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>651900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>612800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>579600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>565300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>557000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>530100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>474200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>455700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>450900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,53 +3044,56 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1937200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1955700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1768500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1559200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1423600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1134600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>968500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>820000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>710200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>676100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>436900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>392500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>321500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>215000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,53 +3162,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44802700</v>
+      </c>
+      <c r="E54" s="3">
         <v>43839500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>43345200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>35693200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33608100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29489400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29934900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26007000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25188700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24258000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19858700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14926100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13951500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10121100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3095,8 +3221,11 @@
       <c r="T54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,53 +3269,54 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8896900</v>
+      </c>
+      <c r="E57" s="3">
         <v>9572500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9755300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7834900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7749600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6871800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7054800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5894400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5931000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5920800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4882200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4127700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3990400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2982500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3195,53 +3326,56 @@
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>26100900</v>
+      </c>
+      <c r="E58" s="3">
         <v>24981700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>24015200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19361500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18221300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15938800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16044100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14131600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13310100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12600100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9670300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8089800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7505700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5497200</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3251,53 +3385,56 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>783300</v>
+      </c>
+      <c r="E59" s="3">
         <v>511900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1467700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1012600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>712200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>360500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>601600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>430900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>308000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>256400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>339100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>234800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>160800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>75900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3307,8 +3444,11 @@
       <c r="T59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3363,53 +3503,56 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1514400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1341200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1059700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1031900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>741000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>633500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>567600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>441400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>495900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>168000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>164900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>169900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>117100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>513600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3419,53 +3562,56 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E62" s="3">
         <v>13600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>80600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>89700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>67900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>59100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>59600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>60600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>64600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>47400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>97700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>69800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>53700</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,53 +3798,56 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>37879300</v>
+      </c>
+      <c r="E66" s="3">
         <v>37036800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36938800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>29803900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27963500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24280900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25044100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>21254300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20450500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19469000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15417600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13022400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12014400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9317200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>8</v>
       </c>
@@ -3699,8 +3857,11 @@
       <c r="T66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,53 +4116,56 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2254800</v>
+      </c>
+      <c r="E72" s="3">
         <v>1716100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2553900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>887800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>546700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>257100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>64600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-45900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-95900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-116800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-128400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-108900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-104800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-117300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4001,8 +4175,11 @@
       <c r="T72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,53 +4352,56 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6923400</v>
+      </c>
+      <c r="E76" s="3">
         <v>6802700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6406400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5889300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5644600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5208500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4890800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4752700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4738200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4789000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4441000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1903700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1937100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>803800</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4225,8 +4411,11 @@
       <c r="T76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>487300</v>
+      </c>
+      <c r="E81" s="3">
         <v>378800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>360900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>303000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>224900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>141800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-297600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-45100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-66100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-34200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-107100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-32600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4618,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E83" s="3">
         <v>18500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2668400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-570600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2706500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3234400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1699800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>94300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>228400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>464300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>78300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1859100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-796200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-47100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-221900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-191600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>564800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>660700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-26800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-30900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-47500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-52100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-46500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-27700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-33600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-14700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-47500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-52100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-46500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-27700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-33600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-38200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-30100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-109300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,172 +5547,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>459700</v>
+      </c>
+      <c r="E100" s="3">
         <v>258200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>327200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>68200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>19900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>105300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>324200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>225600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2541200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>61400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>339000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>394400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-24400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-15600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>291500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-618000</v>
+      </c>
+      <c r="E101" s="3">
         <v>449400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>24300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>148700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>70500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>173600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>41800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-28500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>57000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>78600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>279200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-310400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>505500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-388800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-74700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-143000</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2496700</v>
+      </c>
+      <c r="E102" s="3">
         <v>110200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2709800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2961400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1864600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>138200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>479500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>732400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>262900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>709000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-665700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>461800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-143100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>286500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>149800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>874900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-214100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>NU</t>
   </si>
@@ -656,276 +656,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2848700</v>
+        <v>1537200</v>
       </c>
       <c r="E8" s="3">
-        <v>2735900</v>
+        <v>1462600</v>
       </c>
       <c r="F8" s="3">
-        <v>2404900</v>
+        <v>1275000</v>
       </c>
       <c r="G8" s="3">
-        <v>2136800</v>
+        <v>1206800</v>
       </c>
       <c r="H8" s="3">
-        <v>1868600</v>
+        <v>981800</v>
       </c>
       <c r="I8" s="3">
-        <v>1618700</v>
+        <v>829000</v>
       </c>
       <c r="J8" s="3">
+        <v>709400</v>
+      </c>
+      <c r="K8" s="3">
         <v>1450500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1306900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1157600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>877300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>636000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>480900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>336100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>245100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>202600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>156100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>162300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>729500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>723700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>669200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>594400</v>
-      </c>
-      <c r="H9" s="3">
-        <v>496200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>493000</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>457000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>504400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>455500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>307500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>209400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>130000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>87000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>58100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>70600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>55900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>47900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2119200</v>
+        <v>1537200</v>
       </c>
       <c r="E10" s="3">
-        <v>2012200</v>
+        <v>1462600</v>
       </c>
       <c r="F10" s="3">
-        <v>1735700</v>
+        <v>1275000</v>
       </c>
       <c r="G10" s="3">
-        <v>1542400</v>
+        <v>1206800</v>
       </c>
       <c r="H10" s="3">
-        <v>1372400</v>
+        <v>981800</v>
       </c>
       <c r="I10" s="3">
-        <v>1125700</v>
+        <v>829000</v>
       </c>
       <c r="J10" s="3">
+        <v>709400</v>
+      </c>
+      <c r="K10" s="3">
         <v>993500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>802500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>702100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>569800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>426600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>350900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>249100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>187000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>132000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>100200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>114400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>149800</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,8 +960,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,31 +1082,34 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1124,67 +1144,73 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E15" s="3">
         <v>18300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>19200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>10400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2123300</v>
+        <v>813400</v>
       </c>
       <c r="E17" s="3">
-        <v>2157400</v>
+        <v>737200</v>
       </c>
       <c r="F17" s="3">
-        <v>1845000</v>
+        <v>696500</v>
       </c>
       <c r="G17" s="3">
-        <v>1725200</v>
+        <v>646900</v>
       </c>
       <c r="H17" s="3">
-        <v>1544700</v>
+        <v>570300</v>
       </c>
       <c r="I17" s="3">
-        <v>1375000</v>
+        <v>505000</v>
       </c>
       <c r="J17" s="3">
+        <v>465800</v>
+      </c>
+      <c r="K17" s="3">
         <v>1672300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1301800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1182200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>944900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>724500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>502700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>342600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>298400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>228400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>180700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>157400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>723800</v>
+      </c>
+      <c r="E18" s="3">
         <v>725400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>578500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>559900</v>
       </c>
-      <c r="G18" s="3">
-        <v>411600</v>
-      </c>
       <c r="H18" s="3">
-        <v>323900</v>
+        <v>411500</v>
       </c>
       <c r="I18" s="3">
-        <v>243700</v>
+        <v>324000</v>
       </c>
       <c r="J18" s="3">
+        <v>243600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-221800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-67600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-88500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-53300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-25800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-24600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,31 +1377,32 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1392,101 +1426,107 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-88000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-13200</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>743100</v>
+      </c>
+      <c r="E21" s="3">
         <v>743800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>597000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>576500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>430700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>338000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>256800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-211900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-14200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-60000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-82100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-50900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-110100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-37000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-45900</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1521,126 +1561,135 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>723800</v>
+      </c>
+      <c r="E23" s="3">
         <v>725400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>578500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>559900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>411500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>324000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>243600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-221700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-67700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-88500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-53400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-113800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-37800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>170400</v>
+      </c>
+      <c r="E24" s="3">
         <v>238100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>199700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>199100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>108500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>99100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>101900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>75900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-22600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-22200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-6700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-5300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>553400</v>
+      </c>
+      <c r="E26" s="3">
         <v>487300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>378800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>360900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>303000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>224900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>141800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-297600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-29900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-45000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-66300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-49500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-107100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-32600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>553400</v>
+      </c>
+      <c r="E27" s="3">
         <v>487300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>378800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>360900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>303000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>224900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>141800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-297600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-29700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-45100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-66100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-49500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-107100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-32600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,31 +2119,34 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2100,78 +2170,84 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>88000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>13200</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>553400</v>
+      </c>
+      <c r="E33" s="3">
         <v>487300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>378800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>360900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>303000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>224900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>141800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-297600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-29700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-45100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-66100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-49500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-107100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-32600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>553400</v>
+      </c>
+      <c r="E35" s="3">
         <v>487300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>378800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>360900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>303000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>224900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>141800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-297600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-29700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-45100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-66100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-49500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-107100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-32600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,56 +2484,57 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6537000</v>
+        <v>7645800</v>
       </c>
       <c r="E41" s="3">
-        <v>5736900</v>
+        <v>8530400</v>
       </c>
       <c r="F41" s="3">
-        <v>5068500</v>
+        <v>6033700</v>
       </c>
       <c r="G41" s="3">
-        <v>2662200</v>
+        <v>5923400</v>
       </c>
       <c r="H41" s="3">
-        <v>5233500</v>
+        <v>3213600</v>
       </c>
       <c r="I41" s="3">
-        <v>4178700</v>
+        <v>6175000</v>
       </c>
       <c r="J41" s="3">
+        <v>4310500</v>
+      </c>
+      <c r="K41" s="3">
         <v>3959100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1803600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1079100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>905300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>177000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>167600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>185100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>252600</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2457,31 +2544,34 @@
       <c r="U41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>303000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>326300</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>318300</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>55800</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>101600</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>126000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>108700</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2516,49 +2606,52 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>954000</v>
+        <v>18769900</v>
       </c>
       <c r="E43" s="3">
-        <v>1406000</v>
+        <v>17011700</v>
       </c>
       <c r="F43" s="3">
-        <v>1689000</v>
+        <v>18092300</v>
       </c>
       <c r="G43" s="3">
-        <v>1600700</v>
+        <v>17734200</v>
       </c>
       <c r="H43" s="3">
-        <v>1346600</v>
+        <v>15138500</v>
       </c>
       <c r="I43" s="3">
-        <v>1076700</v>
+        <v>14421300</v>
       </c>
       <c r="J43" s="3">
+        <v>12436700</v>
+      </c>
+      <c r="K43" s="3">
         <v>521700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>381800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>374200</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2575,31 +2668,34 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2634,56 +2730,59 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>128600</v>
+        <v>7297500</v>
       </c>
       <c r="E45" s="3">
-        <v>148300</v>
+        <v>7145500</v>
       </c>
       <c r="F45" s="3">
-        <v>81700</v>
+        <v>7583400</v>
       </c>
       <c r="G45" s="3">
-        <v>84300</v>
+        <v>7823800</v>
       </c>
       <c r="H45" s="3">
-        <v>74000</v>
+        <v>6325300</v>
       </c>
       <c r="I45" s="3">
-        <v>73200</v>
+        <v>3245900</v>
       </c>
       <c r="J45" s="3">
+        <v>3032400</v>
+      </c>
+      <c r="K45" s="3">
         <v>61700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>44900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>59900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>51900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2693,31 +2792,34 @@
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>34016100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>33013900</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>32027700</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>31537300</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>24778900</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>23968200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>19888400</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2752,56 +2854,59 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>34370900</v>
+        <v>11562400</v>
       </c>
       <c r="E47" s="3">
-        <v>33715400</v>
+        <v>8995900</v>
       </c>
       <c r="F47" s="3">
-        <v>33854300</v>
+        <v>8987900</v>
       </c>
       <c r="G47" s="3">
-        <v>29006400</v>
+        <v>9163200</v>
       </c>
       <c r="H47" s="3">
-        <v>24749700</v>
+        <v>8574800</v>
       </c>
       <c r="I47" s="3">
-        <v>22297500</v>
+        <v>7443900</v>
       </c>
       <c r="J47" s="3">
+        <v>7758400</v>
+      </c>
+      <c r="K47" s="3">
         <v>23683700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>22249600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>22212800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>21798200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>18536400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13727100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>12859000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9512800</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2811,56 +2916,59 @@
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>53500</v>
+      </c>
+      <c r="E48" s="3">
         <v>56200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>65500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>69800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>62000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>51700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>46900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>46500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2870,56 +2978,59 @@
       <c r="U48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>798400</v>
+      </c>
+      <c r="E49" s="3">
         <v>703600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>705000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>693400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>675400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>651900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>612800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>579600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>565300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>557000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>530100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>474200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>455700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>450900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,56 +3164,59 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1937200</v>
+        <v>42900</v>
       </c>
       <c r="E52" s="3">
-        <v>1955700</v>
+        <v>95900</v>
       </c>
       <c r="F52" s="3">
-        <v>1768500</v>
+        <v>97700</v>
       </c>
       <c r="G52" s="3">
-        <v>1559200</v>
+        <v>113000</v>
       </c>
       <c r="H52" s="3">
-        <v>1423600</v>
+        <v>42900</v>
       </c>
       <c r="I52" s="3">
-        <v>1134600</v>
+        <v>68900</v>
       </c>
       <c r="J52" s="3">
+        <v>48300</v>
+      </c>
+      <c r="K52" s="3">
         <v>968500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>820000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>710200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>676100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>436900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>392500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>321500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>215000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,56 +3288,59 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48637900</v>
+      </c>
+      <c r="E54" s="3">
         <v>44802700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>43839500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>43345200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35693200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33608100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29489400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29934900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26007000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25188700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24258000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19858700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14926100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13951500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10121100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3224,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,56 +3400,57 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8896900</v>
+        <v>28319100</v>
       </c>
       <c r="E57" s="3">
-        <v>9572500</v>
+        <v>25228600</v>
       </c>
       <c r="F57" s="3">
-        <v>9755300</v>
+        <v>24254900</v>
       </c>
       <c r="G57" s="3">
-        <v>7834900</v>
+        <v>23691100</v>
       </c>
       <c r="H57" s="3">
-        <v>7749600</v>
+        <v>19117200</v>
       </c>
       <c r="I57" s="3">
-        <v>6871800</v>
+        <v>18033700</v>
       </c>
       <c r="J57" s="3">
+        <v>15757700</v>
+      </c>
+      <c r="K57" s="3">
         <v>7054800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5894400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5931000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5920800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4882200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4127700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3990400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2982500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3329,56 +3460,59 @@
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>26100900</v>
+        <v>841500</v>
       </c>
       <c r="E58" s="3">
-        <v>24981700</v>
+        <v>888500</v>
       </c>
       <c r="F58" s="3">
-        <v>24015200</v>
+        <v>754300</v>
       </c>
       <c r="G58" s="3">
-        <v>19361500</v>
+        <v>352200</v>
       </c>
       <c r="H58" s="3">
-        <v>18221300</v>
+        <v>297100</v>
       </c>
       <c r="I58" s="3">
-        <v>15938800</v>
+        <v>229300</v>
       </c>
       <c r="J58" s="3">
+        <v>191500</v>
+      </c>
+      <c r="K58" s="3">
         <v>16044100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14131600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13310100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12600100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9670300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8089800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7505700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5497200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3388,56 +3522,59 @@
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>783300</v>
+        <v>9533500</v>
       </c>
       <c r="E59" s="3">
-        <v>511900</v>
+        <v>9504600</v>
       </c>
       <c r="F59" s="3">
-        <v>1467700</v>
+        <v>9915300</v>
       </c>
       <c r="G59" s="3">
-        <v>1012600</v>
+        <v>11078200</v>
       </c>
       <c r="H59" s="3">
-        <v>712200</v>
+        <v>8713900</v>
       </c>
       <c r="I59" s="3">
-        <v>360500</v>
+        <v>8337600</v>
       </c>
       <c r="J59" s="3">
+        <v>7151000</v>
+      </c>
+      <c r="K59" s="3">
         <v>601600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>430900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>308000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>256400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>339100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>234800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>160800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>75900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3447,31 +3584,34 @@
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>38926300</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>35832600</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>35116100</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>35288400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>28298500</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>26763600</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>23201400</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3506,56 +3646,59 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1514400</v>
+        <v>1311700</v>
       </c>
       <c r="E61" s="3">
-        <v>1341200</v>
+        <v>1518100</v>
       </c>
       <c r="F61" s="3">
-        <v>1059700</v>
+        <v>1345100</v>
       </c>
       <c r="G61" s="3">
-        <v>1031900</v>
+        <v>1063700</v>
       </c>
       <c r="H61" s="3">
-        <v>741000</v>
+        <v>1035600</v>
       </c>
       <c r="I61" s="3">
-        <v>633500</v>
+        <v>744800</v>
       </c>
       <c r="J61" s="3">
+        <v>636500</v>
+      </c>
+      <c r="K61" s="3">
         <v>567600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>441400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>495900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>168000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>164900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>169900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>117100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>513600</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3565,56 +3708,59 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>16300</v>
+        <v>684200</v>
       </c>
       <c r="E62" s="3">
-        <v>13600</v>
+        <v>465800</v>
       </c>
       <c r="F62" s="3">
-        <v>8100</v>
+        <v>508100</v>
       </c>
       <c r="G62" s="3">
-        <v>80600</v>
+        <v>518300</v>
       </c>
       <c r="H62" s="3">
-        <v>89700</v>
+        <v>333400</v>
       </c>
       <c r="I62" s="3">
-        <v>67900</v>
+        <v>315200</v>
       </c>
       <c r="J62" s="3">
+        <v>348000</v>
+      </c>
+      <c r="K62" s="3">
         <v>59100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>59600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>60600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>64600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>47400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>97700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>69800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>53700</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,56 +3956,59 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>40993500</v>
+      </c>
+      <c r="E66" s="3">
         <v>37879300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>37036800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36938800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>29803900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27963500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24280900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25044100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>21254300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20450500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19469000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15417600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13022400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12014400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9317200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>8</v>
       </c>
@@ -3860,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,56 +4290,59 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2254800</v>
+        <v>1748900</v>
       </c>
       <c r="E72" s="3">
-        <v>1716100</v>
+        <v>1195600</v>
       </c>
       <c r="F72" s="3">
-        <v>2553900</v>
+        <v>708300</v>
       </c>
       <c r="G72" s="3">
-        <v>887800</v>
+        <v>329500</v>
       </c>
       <c r="H72" s="3">
-        <v>546700</v>
+        <v>-31400</v>
       </c>
       <c r="I72" s="3">
-        <v>257100</v>
+        <v>-334400</v>
       </c>
       <c r="J72" s="3">
+        <v>-559300</v>
+      </c>
+      <c r="K72" s="3">
         <v>64600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-45900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-95900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-116800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-128400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-108900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-104800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-117300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4178,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,56 +4538,59 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7644300</v>
+      </c>
+      <c r="E76" s="3">
         <v>6923400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6802700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6406400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5889300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5644600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5208500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4890800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4752700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4738200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4789000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4441000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1903700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1937100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>803800</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4414,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>553400</v>
+      </c>
+      <c r="E81" s="3">
         <v>487300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>378800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>360900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>303000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>224900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>141800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-297600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-29700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-45100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-66100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-49500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-107100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-32600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,67 +4817,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>18300</v>
+        <v>13400</v>
       </c>
       <c r="E83" s="3">
-        <v>18500</v>
+        <v>14000</v>
       </c>
       <c r="F83" s="3">
-        <v>16500</v>
+        <v>13200</v>
       </c>
       <c r="G83" s="3">
-        <v>19200</v>
+        <v>9900</v>
       </c>
       <c r="H83" s="3">
-        <v>14000</v>
+        <v>7600</v>
       </c>
       <c r="I83" s="3">
-        <v>13200</v>
+        <v>10400</v>
       </c>
       <c r="J83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="K83" s="3">
         <v>9900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1068900</v>
+      </c>
+      <c r="E89" s="3">
         <v>2668400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-570600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2706500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3234400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1699800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>94300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>228400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-15400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>464300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>78300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1859100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-796200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-47100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-221900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-191600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>564800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>660700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,67 +5275,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-16800</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3">
-        <v>-26800</v>
+        <v>200</v>
       </c>
       <c r="F91" s="3">
-        <v>-30900</v>
+        <v>-200</v>
       </c>
       <c r="G91" s="3">
-        <v>-47500</v>
+        <v>-4800</v>
       </c>
       <c r="H91" s="3">
-        <v>-52100</v>
+        <v>-4100</v>
       </c>
       <c r="I91" s="3">
-        <v>-46500</v>
+        <v>-6800</v>
       </c>
       <c r="J91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-27700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-33600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-38300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5459,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-42500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-26800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-47500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-52100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-46500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-38200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-30100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-109300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,31 +5547,32 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,181 +5793,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-311600</v>
+      </c>
+      <c r="E100" s="3">
         <v>459700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>258200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>327200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>68200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>19900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>105300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>324200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>225600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2541200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>61400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>339000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>394400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-24400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-15600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>291500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-618000</v>
+        <v>-6800</v>
       </c>
       <c r="E101" s="3">
-        <v>449400</v>
+        <v>148700</v>
       </c>
       <c r="F101" s="3">
-        <v>24300</v>
+        <v>70500</v>
       </c>
       <c r="G101" s="3">
-        <v>-6800</v>
+        <v>173600</v>
       </c>
       <c r="H101" s="3">
-        <v>148700</v>
+        <v>41800</v>
       </c>
       <c r="I101" s="3">
-        <v>70500</v>
+        <v>-28500</v>
       </c>
       <c r="J101" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K101" s="3">
         <v>173600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>41800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-28500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>57000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>78600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>279200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-310400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>505500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-388800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-74700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-143000</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-884600</v>
+      </c>
+      <c r="E102" s="3">
         <v>2496700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>110200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2709800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2961400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1864600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>138200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>479500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>732400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>262900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>709000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-665700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>461800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-143100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>286500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>149800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>874900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-214100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>NU</t>
   </si>
@@ -656,165 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1537200</v>
+        <v>1436900</v>
       </c>
       <c r="E8" s="3">
-        <v>1462600</v>
+        <v>1408100</v>
       </c>
       <c r="F8" s="3">
-        <v>1275000</v>
+        <v>1423700</v>
       </c>
       <c r="G8" s="3">
+        <v>1244500</v>
+      </c>
+      <c r="H8" s="3">
         <v>1206800</v>
       </c>
-      <c r="H8" s="3">
-        <v>981800</v>
-      </c>
       <c r="I8" s="3">
-        <v>829000</v>
+        <v>971600</v>
       </c>
       <c r="J8" s="3">
+        <v>824800</v>
+      </c>
+      <c r="K8" s="3">
         <v>709400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1450500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1306900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1157600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>877300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>636000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>480900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>336100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>245100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>202600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>156100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>162300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -839,106 +845,112 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>457000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>504400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>455500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>307500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>209400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>130000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>87000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>58100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>70600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>55900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>47900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1537200</v>
+        <v>1436900</v>
       </c>
       <c r="E10" s="3">
-        <v>1462600</v>
+        <v>1408100</v>
       </c>
       <c r="F10" s="3">
-        <v>1275000</v>
+        <v>1423700</v>
       </c>
       <c r="G10" s="3">
+        <v>1244500</v>
+      </c>
+      <c r="H10" s="3">
         <v>1206800</v>
       </c>
-      <c r="H10" s="3">
-        <v>981800</v>
-      </c>
       <c r="I10" s="3">
-        <v>829000</v>
+        <v>971600</v>
       </c>
       <c r="J10" s="3">
+        <v>824800</v>
+      </c>
+      <c r="K10" s="3">
         <v>709400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>993500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>802500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>702100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>569800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>426600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>350900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>249100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>187000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>132000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>100200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>114400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>149800</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1023,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1111,8 +1130,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1147,70 +1166,76 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E15" s="3">
         <v>19300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>16500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>13200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>10400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>813400</v>
+        <v>669500</v>
       </c>
       <c r="E17" s="3">
-        <v>737200</v>
+        <v>684300</v>
       </c>
       <c r="F17" s="3">
-        <v>696500</v>
+        <v>698300</v>
       </c>
       <c r="G17" s="3">
+        <v>665900</v>
+      </c>
+      <c r="H17" s="3">
         <v>646900</v>
       </c>
-      <c r="H17" s="3">
-        <v>570300</v>
-      </c>
       <c r="I17" s="3">
-        <v>505000</v>
+        <v>560100</v>
       </c>
       <c r="J17" s="3">
+        <v>500800</v>
+      </c>
+      <c r="K17" s="3">
         <v>465800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1672300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1301800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1182200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>944900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>724500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>502700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>342600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>298400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>228400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>180700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>157400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>767500</v>
+      </c>
+      <c r="E18" s="3">
         <v>723800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>725400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>578500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>559900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>411500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>324000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>243600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-221800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-24600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-67600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-88500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-53300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-25800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-24600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,8 +1410,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1404,8 +1437,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1429,81 +1462,87 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-88000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-13200</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>788500</v>
+      </c>
+      <c r="E21" s="3">
         <v>743100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>743800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>597000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>576500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>430700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>338000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>256800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-211900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-14200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-60000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-82100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-50900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-110100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-37000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-45900</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1528,8 +1567,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1564,132 +1603,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>767500</v>
+      </c>
+      <c r="E23" s="3">
         <v>723800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>725400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>578500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>559900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>411500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>324000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>243600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-221700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-67700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-88500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-53400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-113800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-37800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>214800</v>
+      </c>
+      <c r="E24" s="3">
         <v>170400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>238100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>199700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>199100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>108500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>99100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>101900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>75900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-22600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-22200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>12600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-6700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>552600</v>
+      </c>
+      <c r="E26" s="3">
         <v>553400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>487300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>378800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>360900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>303000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>224900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>141800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-297600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-29900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-45000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-66300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-34400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-49500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-107100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-32600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>552600</v>
+      </c>
+      <c r="E27" s="3">
         <v>553400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>487300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>378800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>360900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>303000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>224900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>141800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-297600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-29700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-45100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-66100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-15200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-49500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-107100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-32600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,8 +2188,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2148,8 +2217,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2173,81 +2242,87 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>88000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>13200</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>552600</v>
+      </c>
+      <c r="E33" s="3">
         <v>553400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>487300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>378800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>360900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>303000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>224900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>141800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-297600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-29700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-45100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-66100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-15200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-49500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-107100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-32600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>552600</v>
+      </c>
+      <c r="E35" s="3">
         <v>553400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>487300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>378800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>360900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>303000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>224900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>141800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-297600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-29700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-45100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-66100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-15200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-49500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-107100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-32600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,59 +2570,60 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7645800</v>
+        <v>6893900</v>
       </c>
       <c r="E41" s="3">
-        <v>8530400</v>
+        <v>5515100</v>
       </c>
       <c r="F41" s="3">
-        <v>6033700</v>
+        <v>6943200</v>
       </c>
       <c r="G41" s="3">
+        <v>6033600</v>
+      </c>
+      <c r="H41" s="3">
         <v>5923400</v>
       </c>
-      <c r="H41" s="3">
-        <v>3213600</v>
-      </c>
       <c r="I41" s="3">
-        <v>6175000</v>
+        <v>3208900</v>
       </c>
       <c r="J41" s="3">
+        <v>5743600</v>
+      </c>
+      <c r="K41" s="3">
         <v>4310500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3959100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1803600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1079100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>905300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>177000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>167600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>185100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>252600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2547,35 +2633,38 @@
       <c r="V41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>303000</v>
+        <v>3336500</v>
       </c>
       <c r="E42" s="3">
-        <v>326300</v>
+        <v>2742500</v>
       </c>
       <c r="F42" s="3">
-        <v>318300</v>
+        <v>2697600</v>
       </c>
       <c r="G42" s="3">
-        <v>55800</v>
+        <v>1021400</v>
       </c>
       <c r="H42" s="3">
-        <v>101600</v>
+        <v>635800</v>
       </c>
       <c r="I42" s="3">
-        <v>126000</v>
+        <v>374600</v>
       </c>
       <c r="J42" s="3">
+        <v>825900</v>
+      </c>
+      <c r="K42" s="3">
         <v>108700</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2609,52 +2698,55 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>18769900</v>
+        <v>218800</v>
       </c>
       <c r="E43" s="3">
-        <v>17011700</v>
+        <v>170000</v>
       </c>
       <c r="F43" s="3">
-        <v>18092300</v>
+        <v>22100</v>
       </c>
       <c r="G43" s="3">
-        <v>17734200</v>
+        <v>25800</v>
       </c>
       <c r="H43" s="3">
-        <v>15138500</v>
+        <v>428700</v>
       </c>
       <c r="I43" s="3">
-        <v>14421300</v>
+        <v>352200</v>
       </c>
       <c r="J43" s="3">
+        <v>253800</v>
+      </c>
+      <c r="K43" s="3">
         <v>12436700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>521700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>381800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>374200</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2671,8 +2763,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2697,8 +2792,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2733,59 +2828,62 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7297500</v>
+        <v>79000</v>
       </c>
       <c r="E45" s="3">
-        <v>7145500</v>
+        <v>90700</v>
       </c>
       <c r="F45" s="3">
-        <v>7583400</v>
+        <v>81500</v>
       </c>
       <c r="G45" s="3">
-        <v>7823800</v>
+        <v>66500</v>
       </c>
       <c r="H45" s="3">
-        <v>6325300</v>
+        <v>100200</v>
       </c>
       <c r="I45" s="3">
-        <v>3245900</v>
+        <v>140500</v>
       </c>
       <c r="J45" s="3">
+        <v>133000</v>
+      </c>
+      <c r="K45" s="3">
         <v>3032400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>61700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>44900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>59900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>51900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2795,35 +2893,38 @@
       <c r="V45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>34016100</v>
+        <v>17351700</v>
       </c>
       <c r="E46" s="3">
-        <v>33013900</v>
+        <v>15427800</v>
       </c>
       <c r="F46" s="3">
-        <v>32027700</v>
+        <v>16538900</v>
       </c>
       <c r="G46" s="3">
-        <v>31537300</v>
+        <v>14301700</v>
       </c>
       <c r="H46" s="3">
-        <v>24778900</v>
+        <v>14617300</v>
       </c>
       <c r="I46" s="3">
-        <v>23968200</v>
+        <v>10010000</v>
       </c>
       <c r="J46" s="3">
+        <v>9857200</v>
+      </c>
+      <c r="K46" s="3">
         <v>19888400</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2857,59 +2958,62 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>11562400</v>
+        <v>10271200</v>
       </c>
       <c r="E47" s="3">
-        <v>8995900</v>
+        <v>11035300</v>
       </c>
       <c r="F47" s="3">
-        <v>8987900</v>
+        <v>8170800</v>
       </c>
       <c r="G47" s="3">
-        <v>9163200</v>
+        <v>8398100</v>
       </c>
       <c r="H47" s="3">
-        <v>8574800</v>
+        <v>8642300</v>
       </c>
       <c r="I47" s="3">
-        <v>7443900</v>
+        <v>8339800</v>
       </c>
       <c r="J47" s="3">
+        <v>5530000</v>
+      </c>
+      <c r="K47" s="3">
         <v>7758400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>23683700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>22249600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>22212800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>21798200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>18536400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13727100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>12859000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9512800</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2919,59 +3023,62 @@
       <c r="V47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E48" s="3">
         <v>53500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>56200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>65500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>69800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>62000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>51700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>46900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>46500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>40500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>37200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2981,59 +3088,62 @@
       <c r="V48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>761900</v>
+      </c>
+      <c r="E49" s="3">
         <v>798400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>703600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>705000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>693400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>675400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>651900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>612800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>579600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>565300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>557000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>530100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>474200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>455700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>450900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,59 +3283,62 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>42900</v>
+        <v>432500</v>
       </c>
       <c r="E52" s="3">
-        <v>95900</v>
+        <v>558400</v>
       </c>
       <c r="F52" s="3">
-        <v>97700</v>
+        <v>406400</v>
       </c>
       <c r="G52" s="3">
-        <v>113000</v>
+        <v>347100</v>
       </c>
       <c r="H52" s="3">
-        <v>42900</v>
+        <v>248400</v>
       </c>
       <c r="I52" s="3">
-        <v>68900</v>
+        <v>260700</v>
       </c>
       <c r="J52" s="3">
+        <v>1926300</v>
+      </c>
+      <c r="K52" s="3">
         <v>48300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>968500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>820000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>710200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>676100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>436900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>392500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>321500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>215000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,59 +3413,62 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49931200</v>
+      </c>
+      <c r="E54" s="3">
         <v>48637900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>44802700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>43839500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43345200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>35693200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33608100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29489400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29934900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26007000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25188700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24258000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19858700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14926100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13951500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10121100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3353,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,59 +3530,60 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28855100</v>
+      </c>
+      <c r="E57" s="3">
         <v>28319100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25228600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24254900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23691100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19117200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18033700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15757700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7054800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5894400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5931000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5920800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4882200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4127700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3990400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2982500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3463,59 +3593,62 @@
       <c r="V57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>755200</v>
+      </c>
+      <c r="E58" s="3">
         <v>841500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>888500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>754300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>352200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>297100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>229300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>191500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16044100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14131600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13310100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12600100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9670300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8089800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7505700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5497200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3525,59 +3658,62 @@
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9533500</v>
+        <v>10465100</v>
       </c>
       <c r="E59" s="3">
+        <v>9604700</v>
+      </c>
+      <c r="F59" s="3">
         <v>9504600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9915300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11078200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8713900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8337600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7151000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>601600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>430900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>308000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>256400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>339100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>234800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>160800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>75900</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3587,35 +3723,38 @@
       <c r="V59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>38926300</v>
+        <v>40272200</v>
       </c>
       <c r="E60" s="3">
+        <v>38987900</v>
+      </c>
+      <c r="F60" s="3">
         <v>35832600</v>
       </c>
-      <c r="F60" s="3">
-        <v>35116100</v>
-      </c>
       <c r="G60" s="3">
-        <v>35288400</v>
+        <v>35131700</v>
       </c>
       <c r="H60" s="3">
+        <v>35303200</v>
+      </c>
+      <c r="I60" s="3">
         <v>28298500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26763600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23201400</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3649,59 +3788,62 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1342300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1311700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1518100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1345100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1063700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1035600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>744800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>636500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>567600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>441400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>495900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>168000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>164900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>169900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>117100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>513600</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3711,59 +3853,62 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>684200</v>
+        <v>598000</v>
       </c>
       <c r="E62" s="3">
+        <v>622500</v>
+      </c>
+      <c r="F62" s="3">
         <v>465800</v>
       </c>
-      <c r="F62" s="3">
-        <v>508100</v>
-      </c>
       <c r="G62" s="3">
-        <v>518300</v>
+        <v>492400</v>
       </c>
       <c r="H62" s="3">
+        <v>503500</v>
+      </c>
+      <c r="I62" s="3">
         <v>333400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>315200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>348000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>59100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>59600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>60600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>64600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>47400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>97700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>69800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>53700</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3773,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,59 +4113,62 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>42284100</v>
+      </c>
+      <c r="E66" s="3">
         <v>40993500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>37879300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>37036800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36938800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29803900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27963500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24280900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25044100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>21254300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20450500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19469000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15417600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13022400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12014400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9317200</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4021,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,59 +4463,62 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2280300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1748900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1195600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>708300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>329500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-31400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-334400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-559300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>64600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-45900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-95900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-116800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-128400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-108900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-104800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-117300</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4355,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,59 +4723,62 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7646300</v>
+      </c>
+      <c r="E76" s="3">
         <v>7644300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6923400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6802700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6406400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5889300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5644600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5208500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4890800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4752700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4738200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4789000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4441000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1903700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1937100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>803800</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4603,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>552600</v>
+      </c>
+      <c r="E81" s="3">
         <v>553400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>487300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>378800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>360900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>303000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>224900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>141800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-297600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-29700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-45100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-66100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-15200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-49500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-107100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-32600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>13400</v>
+        <v>16500</v>
       </c>
       <c r="E83" s="3">
+        <v>19200</v>
+      </c>
+      <c r="F83" s="3">
         <v>14000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1068900</v>
+        <v>267800</v>
       </c>
       <c r="E89" s="3">
-        <v>2668400</v>
+        <v>-4186000</v>
       </c>
       <c r="F89" s="3">
-        <v>-570600</v>
+        <v>1548200</v>
       </c>
       <c r="G89" s="3">
-        <v>2706500</v>
+        <v>-1141500</v>
       </c>
       <c r="H89" s="3">
-        <v>-3234400</v>
+        <v>-1631900</v>
       </c>
       <c r="I89" s="3">
-        <v>1699800</v>
+        <v>-4460300</v>
       </c>
       <c r="J89" s="3">
+        <v>-450400</v>
+      </c>
+      <c r="K89" s="3">
         <v>94300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>228400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>464300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>78300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1859100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-796200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-47100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-221900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-191600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>564800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>660700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5495,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-33600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-38300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-247900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-42500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-30900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-47500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-52100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-46500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-33600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-38200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-30100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-109300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5574,8 +5807,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-311600</v>
+        <v>1423700</v>
       </c>
       <c r="E100" s="3">
-        <v>459700</v>
+        <v>2805500</v>
       </c>
       <c r="F100" s="3">
-        <v>258200</v>
+        <v>1580000</v>
       </c>
       <c r="G100" s="3">
-        <v>9900</v>
+        <v>829100</v>
       </c>
       <c r="H100" s="3">
-        <v>327200</v>
+        <v>4348300</v>
       </c>
       <c r="I100" s="3">
-        <v>68200</v>
+        <v>1553200</v>
       </c>
       <c r="J100" s="3">
+        <v>2218300</v>
+      </c>
+      <c r="K100" s="3">
         <v>19900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>105300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>324200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>225600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2541200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>61400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>339000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>394400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-24400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-15600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>291500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>148700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>70500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>173600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>41800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-28500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>173600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>41800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-28500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>57000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>78600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>279200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-310400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>505500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-388800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-74700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-143000</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1540000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-884600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2496700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>110200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2709800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2961400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1864600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>138200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>479500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>732400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>262900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>709000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-665700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>461800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-143100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>286500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>149800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>874900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-214100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
   <si>
     <t>NU</t>
   </si>
@@ -656,171 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1376800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1436900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1408100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1423700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1244500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1206800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>971600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>824800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>709400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1450500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1306900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1157600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>877300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>636000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>480900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>336100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>245100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>202600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>156100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>162300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -848,109 +855,115 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>457000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>504400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>455500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>307500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>209400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>130000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>87000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>58100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>70600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>55900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>47900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1376800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1436900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1408100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1423700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1244500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1206800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>971600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>824800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>709400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>993500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>802500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>702100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>569800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>426600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>350900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>249100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>187000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>132000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>100200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>114400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>149800</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1133,8 +1153,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1169,73 +1189,79 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E15" s="3">
         <v>21100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>13200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>10400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>7700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>581700</v>
+      </c>
+      <c r="E17" s="3">
         <v>669500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>684300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>698300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>665900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>646900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>560100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>500800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>465800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1672300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1301800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1182200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>944900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>724500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>502700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>342600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>298400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>228400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>180700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>157400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>795100</v>
+      </c>
+      <c r="E18" s="3">
         <v>767500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>723800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>725400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>578500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>559900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>411500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>324000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>243600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-221800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-67600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-88500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-53300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-25800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-24600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1444,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1440,8 +1474,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1465,84 +1499,90 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-88000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-13200</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>816400</v>
+      </c>
+      <c r="E21" s="3">
         <v>788500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>743100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>743800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>597000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>576500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>430700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>338000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>256800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-211900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-14200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-60000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-82100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-50900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-110100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-37000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-45900</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1570,8 +1610,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1606,138 +1646,147 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>795100</v>
+      </c>
+      <c r="E23" s="3">
         <v>767500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>723800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>725400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>578500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>559900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>411500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>324000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>243600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-221700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-67700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-88500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-21800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-53400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-113800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-37800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>237900</v>
+      </c>
+      <c r="E24" s="3">
         <v>214800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>170400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>238100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>199700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>199100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>108500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>99100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>101900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>75900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-22600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-6700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-5300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>557200</v>
+      </c>
+      <c r="E26" s="3">
         <v>552600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>553400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>487300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>378800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>360900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>303000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>224900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>141800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-297600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-29900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-45000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-66300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-34400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-15200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-49500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-107100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-32600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>557200</v>
+      </c>
+      <c r="E27" s="3">
         <v>552600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>553400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>487300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>378800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>360900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>303000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>224900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>141800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-297600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-29700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-45100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-66100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-34200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-15200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-49500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-107100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-32600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2258,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2220,8 +2290,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2245,84 +2315,90 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>88000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>13200</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>557200</v>
+      </c>
+      <c r="E33" s="3">
         <v>552600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>553400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>487300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>378800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>360900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>303000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>224900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>141800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-297600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-29700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-45100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-66100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-34200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-15200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-49500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-107100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-32600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>557200</v>
+      </c>
+      <c r="E35" s="3">
         <v>552600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>553400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>487300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>378800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>360900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>303000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>224900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>141800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-297600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-29700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-45100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-66100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-34200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-15200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-49500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-107100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-32600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,62 +2657,63 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7554000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6893900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5515100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6943200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6033600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5923400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3208900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5743600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4310500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3959100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1803600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1079100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>905300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>177000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>167600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>185100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>252600</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2636,38 +2723,41 @@
       <c r="W41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3479000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3336500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2742500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2697600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1021400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>635800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>374600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>825900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>108700</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2701,55 +2791,58 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>651500</v>
+      </c>
+      <c r="E43" s="3">
         <v>218800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>170000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>22100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>25800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>428700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>352200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>253800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12436700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>521700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>381800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>374200</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -2766,8 +2859,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2795,8 +2891,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2831,62 +2927,65 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E45" s="3">
         <v>79000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>90700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>81500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>66500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>140500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>133000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3032400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>61700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>44900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>59900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>51900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>16300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2896,38 +2995,41 @@
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19209200</v>
+      </c>
+      <c r="E46" s="3">
         <v>17351700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15427800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16538900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14301700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14617300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10010000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9857200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19888400</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2961,62 +3063,65 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10213000</v>
+      </c>
+      <c r="E47" s="3">
         <v>10271200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11035300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8170800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8398100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8642300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8339800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5530000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7758400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>23683700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>22249600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>22212800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>21798200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>18536400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13727100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12859000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9512800</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3026,62 +3131,65 @@
       <c r="W47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E48" s="3">
         <v>46200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>53500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>56200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>65500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>69800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>62000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>51700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>46900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>46500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>40500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3091,62 +3199,65 @@
       <c r="W48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>848700</v>
+      </c>
+      <c r="E49" s="3">
         <v>761900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>798400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>703600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>705000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>693400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>675400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>651900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>612800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>579600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>565300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>557000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>530100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>474200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>455700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>450900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,62 +3403,65 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>527200</v>
+      </c>
+      <c r="E52" s="3">
         <v>432500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>558400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>406400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>347100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>248400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>260700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1926300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>48300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>968500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>820000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>710200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>676100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>436900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>392500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>321500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>215000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,62 +3539,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54192500</v>
+      </c>
+      <c r="E54" s="3">
         <v>49931200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>48637900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>44802700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43839500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>43345200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>35693200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33608100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29489400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29934900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26007000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25188700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24258000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19858700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14926100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13951500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10121100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,62 +3661,63 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31564400</v>
+      </c>
+      <c r="E57" s="3">
         <v>28855100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28319100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>25228600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>24254900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23691100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19117200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18033700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15757700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7054800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5894400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5931000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5920800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4882200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4127700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3990400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2982500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3596,62 +3727,65 @@
       <c r="W57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1362900</v>
+      </c>
+      <c r="E58" s="3">
         <v>755200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>841500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>888500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>754300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>352200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>297100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>229300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>191500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16044100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14131600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13310100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12600100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9670300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8089800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7505700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5497200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3661,62 +3795,65 @@
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10602100</v>
+      </c>
+      <c r="E59" s="3">
         <v>10465100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9604700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9504600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9915300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11078200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8713900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8337600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7151000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>601600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>430900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>308000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>256400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>339100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>234800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>160800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>75900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3726,38 +3863,41 @@
       <c r="W59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43728600</v>
+      </c>
+      <c r="E60" s="3">
         <v>40272200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38987900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35832600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35131700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35303200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28298500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26763600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23201400</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3791,62 +3931,65 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>956300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1342300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1311700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1518100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1345100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1063700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1035600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>744800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>636500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>567600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>441400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>495900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>168000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>164900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>169900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>117100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>513600</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -3856,62 +3999,65 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>813300</v>
+      </c>
+      <c r="E62" s="3">
         <v>598000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>622500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>465800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>492400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>503500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>333400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>315200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>348000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>59100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>59600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>60600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>64600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>47400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>97700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>69800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>53700</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,62 +4271,65 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45583600</v>
+      </c>
+      <c r="E66" s="3">
         <v>42284100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>40993500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>37879300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>37036800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36938800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29803900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>27963500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24280900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25044100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21254300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20450500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19469000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15417600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13022400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12014400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9317200</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,62 +4637,65 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2839700</v>
+      </c>
+      <c r="E72" s="3">
         <v>2280300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1748900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1195600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>708300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>329500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-31400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-334400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-559300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>64600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-45900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-95900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-116800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-128400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-108900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-104800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-117300</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,62 +4909,65 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8607900</v>
+      </c>
+      <c r="E76" s="3">
         <v>7646300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7644300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6923400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6802700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6406400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5889300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5644600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5208500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4890800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4752700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4738200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4789000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4441000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1903700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1937100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>803800</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>557200</v>
+      </c>
+      <c r="E81" s="3">
         <v>552600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>553400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>487300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>378800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>360900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>303000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>224900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>141800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-297600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-29700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-45100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-66100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-34200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-15200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-49500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-107100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-32600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,73 +5214,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E83" s="3">
         <v>16500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>19200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1557800</v>
+      </c>
+      <c r="E89" s="3">
         <v>267800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4186000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1548200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1141500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1631900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4460300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-450400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>94300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>228400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>464300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>78300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1859100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-796200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-47100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-221900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-191600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>564800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>660700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5400</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-33600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-38300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-14700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-81400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-247900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-42500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-47500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-52100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-46500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-33600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-38200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-30100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-109300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5810,8 +6044,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,199 +6284,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2473900</v>
+      </c>
+      <c r="E100" s="3">
         <v>1423700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2805500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1580000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>829100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4348300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1553200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2218300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>19900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>105300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>324200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>225600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2541200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>61400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>339000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>394400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-24400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-15600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>291500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>449400</v>
+      </c>
+      <c r="E101" s="3">
         <v>24300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>148700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>70500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>173600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>41800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-28500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>173600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>41800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-28500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>57000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>78600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>279200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-310400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>505500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-388800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-74700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-143000</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1098300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1540000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-884600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2496700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>110200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2709800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2961400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1864600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>138200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>479500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>732400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>262900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>709000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-665700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>461800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-143100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>286500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>149800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>874900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-214100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>NU</t>
   </si>
@@ -656,178 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1376800</v>
+        <v>1626300</v>
       </c>
       <c r="E8" s="3">
+        <v>1377900</v>
+      </c>
+      <c r="F8" s="3">
         <v>1436900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1408100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1423700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1244500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1206800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>971600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>824800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>709400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1450500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1306900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1157600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>877300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>636000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>480900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>336100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>245100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>202600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>156100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>162300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -858,112 +865,118 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>457000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>504400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>455500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>307500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>209400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>130000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>87000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>58100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>70600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>55900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>47900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1376800</v>
+        <v>1626300</v>
       </c>
       <c r="E10" s="3">
+        <v>1377900</v>
+      </c>
+      <c r="F10" s="3">
         <v>1436900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1408100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1423700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1244500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1206800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>971600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>824800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>709400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>993500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>802500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>702100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>569800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>426600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>350900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>249100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>187000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>132000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>100200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>114400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>149800</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1141,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1156,8 +1176,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1192,76 +1212,82 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E15" s="3">
         <v>21300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>18500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>16500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>13200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>10400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>7700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>745900</v>
+      </c>
+      <c r="E17" s="3">
         <v>581700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>669500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>684300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>698300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>665900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>646900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>560100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>500800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>465800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1672300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1301800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1182200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>944900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>724500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>502700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>342600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>298400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>228400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>180700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>157400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>795100</v>
+        <v>880400</v>
       </c>
       <c r="E18" s="3">
+        <v>796200</v>
+      </c>
+      <c r="F18" s="3">
         <v>767500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>723800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>725400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>578500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>559900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>411500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>324000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>243600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-221800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-67600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-88500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-21800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-53300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-25800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-24600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,16 +1478,17 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1100</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
@@ -1477,8 +1511,8 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1502,87 +1536,93 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-88000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-13200</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>887600</v>
+      </c>
+      <c r="E21" s="3">
         <v>816400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>788500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>743100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>743800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>597000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>576500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>430700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>338000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>256800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-211900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-14200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-82100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-16100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-50900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-110100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-37000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-45900</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1613,8 +1653,8 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1649,144 +1689,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>879400</v>
+      </c>
+      <c r="E23" s="3">
         <v>795100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>767500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>723800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>725400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>578500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>559900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>411500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>324000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>243600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-221700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-67700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-88500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-21800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-53400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-113800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-37800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>242400</v>
+      </c>
+      <c r="E24" s="3">
         <v>237900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>214800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>170400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>238100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>199700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>199100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>108500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>99100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>101900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>75900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-22200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-3900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-6700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-5300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>637000</v>
+      </c>
+      <c r="E26" s="3">
         <v>557200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>552600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>553400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>487300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>378800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>360900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>303000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>224900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>141800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-297600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-29900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-66300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-34400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-15200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-49500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-107100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-32600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>636800</v>
+      </c>
+      <c r="E27" s="3">
         <v>557200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>552600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>553400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>487300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>378800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>360900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>303000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>224900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>141800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-297600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-29700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-45100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-66100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-34200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-15200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-49500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-107100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-32600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,16 +2328,19 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1100</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
@@ -2293,8 +2363,8 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2318,87 +2388,93 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>88000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>13200</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>636800</v>
+      </c>
+      <c r="E33" s="3">
         <v>557200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>552600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>553400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>487300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>378800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>360900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>303000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>224900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>141800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-297600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-29700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-45100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-66100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-34200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-15200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-49500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-107100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-32600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>636800</v>
+      </c>
+      <c r="E35" s="3">
         <v>557200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>552600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>553400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>487300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>378800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>360900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>303000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>224900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>141800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-297600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-29700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-45100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-66100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-34200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-15200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-49500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-107100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-32600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,65 +2744,66 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8943700</v>
+      </c>
+      <c r="E41" s="3">
         <v>7554000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6893900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5515100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6943200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6033600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5923400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3208900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5743600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4310500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3959100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1803600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1079100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>905300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>177000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>167600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>185100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>252600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2726,41 +2813,44 @@
       <c r="X41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5179300</v>
+      </c>
+      <c r="E42" s="3">
         <v>3479000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3336500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2742500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2697600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1021400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>635800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>374600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>825900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>108700</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -2794,58 +2884,61 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>701200</v>
+      </c>
+      <c r="E43" s="3">
         <v>651500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>218800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>170000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>428700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>352200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>253800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12436700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>521700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>381800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>374200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -2862,8 +2955,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2894,8 +2990,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2930,65 +3026,68 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E45" s="3">
         <v>63400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>79000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>90700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>81500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>66500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>140500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>133000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3032400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>61700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>44900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>59900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>51900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>16000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2998,41 +3097,44 @@
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23227400</v>
+      </c>
+      <c r="E46" s="3">
         <v>19209200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17351700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15427800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16538900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14301700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14617300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10010000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9857200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19888400</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3066,65 +3168,68 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10213000</v>
+        <v>11544800</v>
       </c>
       <c r="E47" s="3">
+        <v>10205900</v>
+      </c>
+      <c r="F47" s="3">
         <v>10271200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11035300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8170800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8398100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8642300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8339800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5530000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7758400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>23683700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>22249600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>22212800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>21798200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>18536400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13727100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12859000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>9512800</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3134,65 +3239,68 @@
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E48" s="3">
         <v>46100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>46200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>53500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>56200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>65500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>69800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>62000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>46900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>46500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>37900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>40500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>37200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>17900</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3202,65 +3310,68 @@
       <c r="X48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>924600</v>
+      </c>
+      <c r="E49" s="3">
         <v>848700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>761900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>798400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>703600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>705000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>693400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>675400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>651900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>612800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>579600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>565300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>557000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>530100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>474200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>455700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>450900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>13000</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,65 +3523,68 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>527200</v>
+        <v>689900</v>
       </c>
       <c r="E52" s="3">
+        <v>534400</v>
+      </c>
+      <c r="F52" s="3">
         <v>432500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>558400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>406400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>347100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>248400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>260700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1926300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>48300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>968500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>820000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>710200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>676100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>436900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>392500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>321500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>215000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,65 +3665,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>62730100</v>
+      </c>
+      <c r="E54" s="3">
         <v>54192500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>49931200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>48637900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>44802700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>43839500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43345200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>35693200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33608100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29489400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29934900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26007000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25188700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>24258000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19858700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14926100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13951500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10121100</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,65 +3792,66 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36640200</v>
+      </c>
+      <c r="E57" s="3">
         <v>31564400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28855100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28319100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>25228600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24254900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23691100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19117200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18033700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15757700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7054800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5894400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5931000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5920800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4882200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4127700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3990400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2982500</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3730,65 +3861,68 @@
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2436300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1362900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>755200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>841500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>888500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>754300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>352200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>297100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>229300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>191500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>16044100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14131600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13310100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12600100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9670300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>8089800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7505700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5497200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3798,65 +3932,68 @@
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10602100</v>
+        <v>8554800</v>
       </c>
       <c r="E59" s="3">
-        <v>10465100</v>
+        <v>7767500</v>
       </c>
       <c r="F59" s="3">
+        <v>10396500</v>
+      </c>
+      <c r="G59" s="3">
         <v>9604700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9504600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9915300</v>
       </c>
-      <c r="I59" s="3">
-        <v>11078200</v>
-      </c>
       <c r="J59" s="3">
+        <v>10994700</v>
+      </c>
+      <c r="K59" s="3">
         <v>8713900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8337600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7151000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>601600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>430900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>308000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>256400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>339100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>234800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>160800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>75900</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3866,41 +4003,44 @@
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>43728600</v>
+        <v>47957700</v>
       </c>
       <c r="E60" s="3">
+        <v>40894100</v>
+      </c>
+      <c r="F60" s="3">
         <v>40272200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38987900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35832600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35131700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35303200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28298500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26763600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23201400</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3934,65 +4074,68 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1055800</v>
+      </c>
+      <c r="E61" s="3">
         <v>956300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1342300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1311700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1518100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1345100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1063700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1035600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>744800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>636500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>567600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>441400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>495900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>168000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>164900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>169900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>117100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>513600</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4002,65 +4145,68 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>813300</v>
+        <v>4034200</v>
       </c>
       <c r="E62" s="3">
+        <v>3647800</v>
+      </c>
+      <c r="F62" s="3">
         <v>598000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>622500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>465800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>492400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>503500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>333400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>315200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>348000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>59100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>59600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>60600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>64600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>47400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>97700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>69800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>53700</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,65 +4429,68 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53154000</v>
+      </c>
+      <c r="E66" s="3">
         <v>45583600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>42284100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>40993500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>37879300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37036800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36938800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29803900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27963500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24280900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25044100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21254300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20450500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19469000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15417600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13022400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12014400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9317200</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,65 +4811,68 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3476600</v>
+      </c>
+      <c r="E72" s="3">
         <v>2839700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2280300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1748900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1195600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>708300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>329500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-31400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-334400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-559300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>64600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-45900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-95900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-116800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-128400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-108900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-104800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-117300</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,65 +5095,68 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9574800</v>
+      </c>
+      <c r="E76" s="3">
         <v>8607900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7646300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7644300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6923400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6802700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6406400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5889300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5644600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5208500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4890800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4752700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4738200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4789000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4441000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1903700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1937100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>803800</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>636800</v>
+      </c>
+      <c r="E81" s="3">
         <v>557200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>552600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>553400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>487300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>378800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>360900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>303000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>224900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>141800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-297600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-29700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-45100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-66100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-34200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-15200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-49500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-107100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-32600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5413,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E83" s="3">
         <v>18500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2149100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1557800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>267800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4186000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1548200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1141500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1631900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4460300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-450400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>94300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>228400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>464300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>78300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1859100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-796200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-47100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-221900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-191600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>564800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>660700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5400</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
         <v>200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-33600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-38300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-71500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-81400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-247900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-42500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-26800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-30900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-47500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-52100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-46500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-33600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-38200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-30100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-109300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6047,8 +6281,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,208 +6530,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5138200</v>
+      </c>
+      <c r="E100" s="3">
         <v>2473900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1423700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2805500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1580000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>829100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4348300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1553200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2218300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>19900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>105300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>324200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>225600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2541200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>61400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>339000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>394400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-24400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-15600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>291500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-618000</v>
+      </c>
+      <c r="E101" s="3">
         <v>449400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>24300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>148700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>70500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>173600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>41800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-28500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>173600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>41800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-28500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>57000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>78600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>279200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-310400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>505500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-388800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-74700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-143000</v>
       </c>
     </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2985000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1098300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1540000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-884600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2496700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>110200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2709800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2961400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1864600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>138200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>479500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>732400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>262900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>709000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-665700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>461800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-143100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>286500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>149800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>874900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-214100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>NU</t>
   </si>
@@ -656,192 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2067400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1919500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1626300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1377900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1436900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1408100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1423700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1244500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1206800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>971600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>824800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>709400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1450500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1306900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1157600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>877300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>636000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>480900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>336100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>245100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>202600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>156100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>162300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -878,118 +884,124 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
         <v>457000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>504400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>455500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>307500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>209400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>130000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>87000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>58100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>70600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>55900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>47900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2067400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1919500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1626300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1377900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1436900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1408100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1423700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1244500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1206800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>971600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>824800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>709400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>993500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>802500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>702100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>569800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>426600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>350900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>249100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>187000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>132000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>100200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>114400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>149800</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1202,8 +1221,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1238,82 +1257,88 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E15" s="3">
         <v>10600</v>
       </c>
-      <c r="E15" s="3">
-        <v>8200</v>
-      </c>
       <c r="F15" s="3">
-        <v>21300</v>
+        <v>7300</v>
       </c>
       <c r="G15" s="3">
-        <v>21100</v>
+        <v>9100</v>
       </c>
       <c r="H15" s="3">
+        <v>47900</v>
+      </c>
+      <c r="I15" s="3">
         <v>15600</v>
       </c>
-      <c r="I15" s="3">
-        <v>18300</v>
-      </c>
       <c r="J15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K15" s="3">
         <v>18500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>19200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>9900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>7600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>10400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>989400</v>
+      </c>
+      <c r="E17" s="3">
         <v>802100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>745900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>581700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>669500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>684300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>698300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>665900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>646900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>560100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>465800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1672300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1301800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1182200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>944900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>724500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>502700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>342600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>298400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>228400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>180700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>157400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1078100</v>
+      </c>
+      <c r="E18" s="3">
         <v>1117500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>880400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>796200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>767500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>723800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>725400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>578500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>559900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>411500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>324000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>243600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-221800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-67600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-88500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-21800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-53300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-25800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-24600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,23 +1545,24 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1100</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1551,8 +1584,8 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1576,93 +1609,99 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-88000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1148700</v>
+      </c>
+      <c r="E21" s="3">
         <v>1126800</v>
       </c>
-      <c r="E21" s="3">
-        <v>887600</v>
-      </c>
       <c r="F21" s="3">
-        <v>816400</v>
+        <v>886700</v>
       </c>
       <c r="G21" s="3">
-        <v>788500</v>
+        <v>804200</v>
       </c>
       <c r="H21" s="3">
+        <v>815300</v>
+      </c>
+      <c r="I21" s="3">
         <v>739400</v>
       </c>
-      <c r="I21" s="3">
-        <v>743800</v>
-      </c>
       <c r="J21" s="3">
+        <v>730000</v>
+      </c>
+      <c r="K21" s="3">
         <v>597000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>576500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>430700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>338000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>256800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-211900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-14200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-60000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-82100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-16100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-50900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-110100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-37000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-45900</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1699,8 +1738,8 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1735,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1077700</v>
+      </c>
+      <c r="E23" s="3">
         <v>1116300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>879400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>795100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>767500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>723800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>725400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>578500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>559900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>411500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>324000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>243600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-221700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-67700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-88500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-21800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-53400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-113800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-37800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>182900</v>
+      </c>
+      <c r="E24" s="3">
         <v>333600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>242400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>237900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>214800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>170400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>238100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>199700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>199100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>108500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>99100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>101900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>75900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-22600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-22200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>12600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-3900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-6700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>894800</v>
+      </c>
+      <c r="E26" s="3">
         <v>782700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>637000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>557200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>552600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>553400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>487300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>378800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>360900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>303000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>224900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>141800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-297600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-29900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-45000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-66300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-34400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-15200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-49500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-107100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-32600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>892400</v>
+      </c>
+      <c r="E27" s="3">
         <v>782500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>636800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>557200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>552600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>553400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>487300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>378800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>360900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>303000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>224900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>141800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-297600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-29700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-45100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-66100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-34200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-15200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-49500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-107100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-32600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,23 +2467,26 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1100</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>8</v>
       </c>
@@ -2439,8 +2508,8 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -2464,93 +2533,99 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>88000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>13200</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>892400</v>
+      </c>
+      <c r="E33" s="3">
         <v>782500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>636800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>557200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>552600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>553400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>487300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>378800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>360900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>303000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>224900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>141800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-297600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-29700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-45100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-66100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-34200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-15200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-49500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-107100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-32600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>892400</v>
+      </c>
+      <c r="E35" s="3">
         <v>782500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>636800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>557200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>552600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>553400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>487300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>378800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>360900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>303000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>224900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>141800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-297600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-29700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-45100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-66100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-34200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-15200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-49500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-107100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-32600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,71 +2917,72 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11392100</v>
+      </c>
+      <c r="E41" s="3">
         <v>9153200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8943700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7554000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6893900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5515100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6943200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6033600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5923400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3208900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5743600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4310500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3959100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1803600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1079100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>905300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>177000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>167600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>185100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>252600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2906,47 +2992,50 @@
       <c r="Z41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4939900</v>
+      </c>
+      <c r="E42" s="3">
         <v>5529900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5179300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3479000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3336500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2742500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2697600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1021400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>635800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>374600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>825900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>108700</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2980,64 +3069,67 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>748800</v>
+      </c>
+      <c r="E43" s="3">
         <v>756900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>701200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>651500</v>
       </c>
-      <c r="G43" s="3">
-        <v>218800</v>
-      </c>
       <c r="H43" s="3">
+        <v>254800</v>
+      </c>
+      <c r="I43" s="3">
         <v>170000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>22100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>428700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>352200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>253800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12436700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>521700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>381800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>374200</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -3054,8 +3146,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3092,8 +3187,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3128,71 +3223,74 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>119200</v>
+      </c>
+      <c r="E45" s="3">
         <v>108300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>96000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>63400</v>
       </c>
-      <c r="G45" s="3">
-        <v>79000</v>
-      </c>
       <c r="H45" s="3">
+        <v>85900</v>
+      </c>
+      <c r="I45" s="3">
         <v>90700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>81500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>66500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>140500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>133000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3032400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>61700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>44900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>59900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>51900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>16000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>16300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3202,47 +3300,50 @@
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26830600</v>
+      </c>
+      <c r="E46" s="3">
         <v>23806600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23227400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19209200</v>
       </c>
-      <c r="G46" s="3">
-        <v>17351700</v>
-      </c>
       <c r="H46" s="3">
+        <v>17345600</v>
+      </c>
+      <c r="I46" s="3">
         <v>15427800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16538900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14301700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14617300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10010000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9857200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>19888400</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3276,71 +3377,74 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15061100</v>
+      </c>
+      <c r="E47" s="3">
         <v>13277100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11544800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10205900</v>
       </c>
-      <c r="G47" s="3">
-        <v>10271200</v>
-      </c>
       <c r="H47" s="3">
+        <v>10271500</v>
+      </c>
+      <c r="I47" s="3">
         <v>11035300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8170800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8398100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8642300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8339800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5530000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7758400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>23683700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>22249600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>22212800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>21798200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>18536400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13727100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12859000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9512800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3350,71 +3454,74 @@
       <c r="Z47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E48" s="3">
         <v>45800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>46700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>46100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>53500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>56200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>65500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>69800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>62000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>51700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>46900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>46500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>37900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>40500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>37200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>17900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3424,71 +3531,74 @@
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1011000</v>
+      </c>
+      <c r="E49" s="3">
         <v>985300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>924600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>848700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>761900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>798400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>703600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>705000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>693400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>675400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>651900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>612800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>579600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>565300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>557000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>530100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>474200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>455700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>450900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>13000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3498,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,71 +3762,74 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>411200</v>
+      </c>
+      <c r="E52" s="3">
         <v>951000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>689900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>534400</v>
       </c>
-      <c r="G52" s="3">
-        <v>432500</v>
-      </c>
       <c r="H52" s="3">
+        <v>474300</v>
+      </c>
+      <c r="I52" s="3">
         <v>558400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>406400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>347100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>248400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>260700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1926300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>48300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>968500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>820000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>710200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>676100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>436900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>392500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>321500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>215000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3720,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,71 +3916,74 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>74893900</v>
+      </c>
+      <c r="E54" s="3">
         <v>68362800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>62730100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>54192500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>49931200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>48637900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44802700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>43839500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43345200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35693200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33608100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29489400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29934900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26007000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25188700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>24258000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>19858700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14926100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13951500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10121100</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3868,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,71 +4053,72 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>41925100</v>
+      </c>
+      <c r="E57" s="3">
         <v>38775900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36640200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31564400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28855100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28319100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>25228600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24254900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23691100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19117200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18033700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15757700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7054800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5894400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5931000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5920800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4882200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4127700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3990400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2982500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3998,71 +4128,74 @@
       <c r="Z57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3375200</v>
+      </c>
+      <c r="E58" s="3">
         <v>3527800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2436300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1362900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>755200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>841500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>888500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>754300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>352200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>297100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>229300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>191500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>16044100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14131600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>13310100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12600100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>9670300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8089800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7505700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5497200</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4072,71 +4205,74 @@
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15001400</v>
+      </c>
+      <c r="E59" s="3">
         <v>9495700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8554800</v>
       </c>
-      <c r="F59" s="3">
-        <v>7767500</v>
-      </c>
       <c r="G59" s="3">
+        <v>487300</v>
+      </c>
+      <c r="H59" s="3">
         <v>10396500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9604700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9504600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9915300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10994700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8713900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8337600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7151000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>601600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>430900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>308000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>256400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>339100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>234800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>160800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>75900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4146,47 +4282,50 @@
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>60651900</v>
+      </c>
+      <c r="E60" s="3">
         <v>52128400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>47957700</v>
       </c>
-      <c r="F60" s="3">
-        <v>40894100</v>
-      </c>
       <c r="G60" s="3">
+        <v>33613900</v>
+      </c>
+      <c r="H60" s="3">
         <v>40272200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>38987900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35832600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35131700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35303200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28298500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26763600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23201400</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4220,71 +4359,74 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1902000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1251500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1055800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>956300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1342300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1311700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1518100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1345100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1063700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1035600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>744800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>636500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>567600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>441400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>495900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>168000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>164900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>169900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>117100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>513600</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4294,71 +4436,74 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>941000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4319300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4034200</v>
       </c>
-      <c r="F62" s="3">
-        <v>3647800</v>
-      </c>
       <c r="G62" s="3">
+        <v>10928000</v>
+      </c>
+      <c r="H62" s="3">
         <v>598000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>622500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>465800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>492400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>503500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>333400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>315200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>348000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>59100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>59600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>60600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>64600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>47400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>97700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>69800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>53700</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4368,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,71 +4744,74 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>63572300</v>
+      </c>
+      <c r="E66" s="3">
         <v>57809300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53154000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45583600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>42284100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>40993500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>37879300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37036800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36938800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29803900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27963500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>24280900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25044100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21254300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20450500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19469000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15417600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13022400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12014400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9317200</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4664,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,71 +5158,74 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5151400</v>
+      </c>
+      <c r="E72" s="3">
         <v>4259100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3476600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2839700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2280300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1748900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1195600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>708300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>329500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-31400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-334400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-559300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>64600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-45900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-95900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-116800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-128400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-108900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-104800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-117300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5062,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,71 +5466,74 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11290900</v>
+      </c>
+      <c r="E76" s="3">
         <v>10552000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9574800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8607900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7646300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7644300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6923400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6802700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6406400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5889300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5644600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5208500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4890800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4752700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4738200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4789000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4441000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1903700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1937100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>803800</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5358,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>892400</v>
+      </c>
+      <c r="E81" s="3">
         <v>782500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>636800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>557200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>552600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>553400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>487300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>378800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>360900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>303000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>224900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>141800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-297600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-29700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-45100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-66100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-34200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-15200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-49500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-107100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-32600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,82 +5810,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E83" s="3">
         <v>10700</v>
       </c>
-      <c r="E83" s="3">
-        <v>-4800</v>
-      </c>
       <c r="F83" s="3">
-        <v>18500</v>
+        <v>4600</v>
       </c>
       <c r="G83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H83" s="3">
         <v>16500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>19200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2682700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2971300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2149100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1557800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>267800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4186000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1548200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1141500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1631900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4460300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-450400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>94300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>228400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>464300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>78300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1859100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-796200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-47100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-221900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-191600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>564800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>660700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,82 +6378,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5400</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
         <v>200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-33600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-38300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-64100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-125300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-71500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-81400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-247900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-42500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-47500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-52100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-46500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-33600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-27700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-38200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-30100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-109300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-10600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6521,8 +6754,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,226 +7021,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4797500</v>
+      </c>
+      <c r="E100" s="3">
         <v>2741900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5138200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2473900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1423700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2805500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1580000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>829100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4348300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1553200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2218300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>19900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>105300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>324200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>225600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2541200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>61400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>339000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>394400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-24400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-15600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>291500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E101" s="3">
         <v>538400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-618000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>449400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>24300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-6800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>148700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>70500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>173600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>41800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-28500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>173600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>41800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-28500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>57000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>78600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>279200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-310400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>505500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-388800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-74700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-143000</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2107900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-373200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2985000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1098300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1540000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-884600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2496700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>110200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2709800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2961400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1864600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>138200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>479500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>732400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>262900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>709000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-665700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>461800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-143100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>286500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>149800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>874900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-214100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
   <si>
     <t>NU</t>
   </si>
@@ -656,198 +656,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1980800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2067400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1919500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1626300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1377900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1436900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1408100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1423700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1244500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1206800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>971600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>824800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>709400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1450500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1306900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1157600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>877300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>636000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>480900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>336100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>245100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>202600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>156100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>162300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -887,121 +894,127 @@
       <c r="O9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
         <v>457000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>504400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>455500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>307500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>209400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>130000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>87000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>58100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>70600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>55900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>47900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1980800</v>
+      </c>
+      <c r="E10" s="3">
         <v>2067400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1919500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1626300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1377900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1436900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1408100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1423700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1244500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1206800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>971600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>824800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>709400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>993500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>802500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>702100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>569800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>426600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>350900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>249100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>187000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>132000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>100200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>114400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>149800</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1224,8 +1244,8 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1260,85 +1280,91 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E15" s="3">
         <v>71000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>47900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>15600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>18500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>19200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>9900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>7600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>10400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>6400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>5700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1025400</v>
+      </c>
+      <c r="E17" s="3">
         <v>989400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>802100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>745900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>581700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>669500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>684300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>698300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>665900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>646900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>560100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>465800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1672300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1301800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1182200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>944900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>724500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>502700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>342600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>298400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>228400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>180700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>157400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>955300</v>
+      </c>
+      <c r="E18" s="3">
         <v>1078100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1117500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>880400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>796200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>767500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>723800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>725400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>578500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>559900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>411500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>324000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>243600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-221800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-24600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-67600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-88500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-21800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-53300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-25800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-24600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,26 +1579,27 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1587,8 +1621,8 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1612,96 +1646,102 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-88000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>966100</v>
+      </c>
+      <c r="E21" s="3">
         <v>1148700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1126800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>886700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>804200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>815300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>739400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>730000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>597000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>576500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>430700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>338000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>256800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-211900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-14200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-60000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-82100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-16100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-50900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-110100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-37000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-45900</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1741,8 +1781,8 @@
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1777,162 +1817,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>954300</v>
+      </c>
+      <c r="E23" s="3">
         <v>1077700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1116300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>879400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>795100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>767500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>723800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>725400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>578500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>559900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>411500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>324000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>243600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-221700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-24600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-67700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-88500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-21800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-53400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-113800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-37800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>82900</v>
+      </c>
+      <c r="E24" s="3">
         <v>182900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>333600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>242400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>237900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>214800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>170400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>238100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>199700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>199100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>108500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>99100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>101900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>75900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-22600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-22200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>871400</v>
+      </c>
+      <c r="E26" s="3">
         <v>894800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>782700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>637000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>557200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>552600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>553400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>487300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>378800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>360900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>303000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>224900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>141800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-297600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-29900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-45000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-66300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-34400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-15200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-49500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-107100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-32600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>872100</v>
+      </c>
+      <c r="E27" s="3">
         <v>892400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>782500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>636800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>557200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>552600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>553400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>487300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>378800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>360900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>303000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>224900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>141800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-297600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-29700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-45100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-66100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-34200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-15200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-49500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-107100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-32600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,26 +2537,29 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
@@ -2511,8 +2581,8 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2536,96 +2606,102 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>88000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>13200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>872100</v>
+      </c>
+      <c r="E33" s="3">
         <v>892400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>782500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>636800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>557200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>552600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>553400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>487300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>378800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>360900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>303000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>224900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>141800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-297600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-29700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-45100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-66100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-34200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-15200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-49500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-107100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-32600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>872100</v>
+      </c>
+      <c r="E35" s="3">
         <v>892400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>782500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>636800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>557200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>552600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>553400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>487300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>378800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>360900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>303000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>224900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>141800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-297600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-29700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-45100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-66100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-34200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-15200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-49500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-107100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-32600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,74 +3004,75 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10173100</v>
+      </c>
+      <c r="E41" s="3">
         <v>11392100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9153200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8943700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7554000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6893900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5515100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6943200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6033600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5923400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3208900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5743600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4310500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3959100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1803600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1079100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>905300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>177000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>167600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>185100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>252600</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2995,50 +3082,53 @@
       <c r="AA41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5733600</v>
+      </c>
+      <c r="E42" s="3">
         <v>4939900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5529900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5179300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3479000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3336500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2742500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2697600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1021400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>635800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>374600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>825900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>108700</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -3072,67 +3162,70 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>844200</v>
+      </c>
+      <c r="E43" s="3">
         <v>748800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>756900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>701200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>651500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>254800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>170000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>22100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>428700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>352200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>253800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12436700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>521700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>381800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>374200</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3149,8 +3242,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3190,8 +3286,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3226,74 +3322,77 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>95700</v>
+      </c>
+      <c r="E45" s="3">
         <v>119200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>108300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>96000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>63400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>85900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>90700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>81500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>66500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>140500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>133000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3032400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>61700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>44900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>59900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>51900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>16000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>16300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9100</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3303,50 +3402,53 @@
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26138000</v>
+      </c>
+      <c r="E46" s="3">
         <v>26830600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23806600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23227400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19209200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17345600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15427800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16538900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14301700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14617300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10010000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9857200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>19888400</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3380,74 +3482,77 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13752500</v>
+      </c>
+      <c r="E47" s="3">
         <v>15061100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>13277100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11544800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10205900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10271500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11035300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8170800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8398100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8642300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8339800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5530000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7758400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>23683700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>22249600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>22212800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>21798200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>18536400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13727100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12859000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9512800</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3457,74 +3562,77 @@
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E48" s="3">
         <v>49800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>46700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>46200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>53500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>56200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>65500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>69800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>62000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>51700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>46900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>46500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>37900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>40500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>37200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>17900</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3534,74 +3642,77 @@
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1109600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1011000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>985300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>924600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>848700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>761900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>798400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>703600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>705000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>693400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>675400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>651900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>612800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>579600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>565300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>557000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>530100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>474200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>455700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>450900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>13000</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,74 +3882,77 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1081400</v>
+      </c>
+      <c r="E52" s="3">
         <v>411200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>951000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>689900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>534400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>474300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>558400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>406400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>347100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>248400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>260700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1926300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>48300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>968500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>820000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>710200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>676100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>436900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>392500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>321500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>215000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,74 +4042,77 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>77456400</v>
+      </c>
+      <c r="E54" s="3">
         <v>74893900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>68362800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>62730100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>54192500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>49931200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>48637900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44802700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43839500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>43345200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35693200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33608100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29489400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29934900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26007000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25188700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>24258000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>19858700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14926100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13951500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10121100</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,74 +4184,75 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42448100</v>
+      </c>
+      <c r="E57" s="3">
         <v>41925100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>38775900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>36640200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31564400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28855100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28319100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>25228600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24254900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>23691100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19117200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18033700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15757700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7054800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5894400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5931000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5920800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4882200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4127700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3990400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2982500</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4131,74 +4262,77 @@
       <c r="AA57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4283100</v>
+      </c>
+      <c r="E58" s="3">
         <v>3375200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3527800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2436300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1362900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>755200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>841500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>888500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>754300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>352200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>297100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>229300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>191500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16044100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14131600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>13310100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>12600100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>9670300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>8089800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7505700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5497200</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4208,74 +4342,77 @@
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14756200</v>
+      </c>
+      <c r="E59" s="3">
         <v>15001400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9495700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8554800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>487300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10396500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9604700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9504600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9915300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10994700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8713900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8337600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7151000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>601600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>430900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>308000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>256400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>339100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>234800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>160800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>75900</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4285,50 +4422,53 @@
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>61933700</v>
+      </c>
+      <c r="E60" s="3">
         <v>60651900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>52128400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47957700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33613900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>40272200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>38987900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35832600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35131700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35303200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28298500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26763600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23201400</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4362,74 +4502,77 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1864300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1902000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1251500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1055800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>956300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1342300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1311700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1518100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1345100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1063700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1035600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>744800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>636500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>567600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>441400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>495900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>168000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>164900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>169900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>117100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>513600</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4439,74 +4582,77 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>982800</v>
+      </c>
+      <c r="E62" s="3">
         <v>941000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4319300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4034200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10928000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>598000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>622500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>465800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>492400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>503500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>333400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>315200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>348000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>59100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>59600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>60600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>64600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>47400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>97700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>69800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>53700</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,74 +4902,77 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>64864600</v>
+      </c>
+      <c r="E66" s="3">
         <v>63572300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57809300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53154000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45583600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>42284100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>40993500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37879300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37036800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36938800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29803900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27963500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24280900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25044100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21254300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20450500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19469000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15417600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13022400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12014400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9317200</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,74 +5332,77 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6023700</v>
+      </c>
+      <c r="E72" s="3">
         <v>5151400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4259100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3476600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2839700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2280300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1748900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1195600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>708300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>329500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-31400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-334400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-559300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>64600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-45900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-95900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-116800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-128400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-108900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-104800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-117300</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,74 +5652,77 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12588800</v>
+      </c>
+      <c r="E76" s="3">
         <v>11290900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10552000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9574800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8607900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7646300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7644300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6923400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6802700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6406400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5889300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5644600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5208500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4890800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4752700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4738200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4789000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4441000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1903700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1937100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>803800</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>872100</v>
+      </c>
+      <c r="E81" s="3">
         <v>892400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>782500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>636800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>557200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>552600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>553400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>487300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>378800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>360900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>303000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>224900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>141800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-297600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-29700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-45100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-66100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-34200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-15200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-49500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-107100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-32600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,85 +6009,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E83" s="3">
         <v>6300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>19200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>10400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>6400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1729400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2682700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2971300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2149100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1557800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>267800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4186000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1548200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1141500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1631900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4460300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-450400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>94300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>228400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>464300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>78300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1859100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-796200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-47100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-221900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-191600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>564800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>660700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5400</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-33600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-38300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-14700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-75200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-64100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-125300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-71500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-81400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-247900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-42500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-47500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-52100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-46500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-33600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-27700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-38200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-30100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-109300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-10600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6757,8 +6991,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,235 +7267,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>435300</v>
+      </c>
+      <c r="E100" s="3">
         <v>4797500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2741900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5138200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2473900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1423700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2805500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1580000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>829100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4348300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1553200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2218300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>19900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>105300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>324200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>225600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2541200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>61400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>339000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>394400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-15600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>291500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>263500</v>
+      </c>
+      <c r="E101" s="3">
         <v>96400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>538400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-618000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>449400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>24300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>148700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>70500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>173600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>41800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-28500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>173600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>41800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-28500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>57000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>78600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>279200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-310400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>505500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-388800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-74700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-143000</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1083200</v>
+      </c>
+      <c r="E102" s="3">
         <v>2107900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-373200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2985000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1098300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1540000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-884600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2496700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>110200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2709800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2961400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1864600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>138200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>479500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>732400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>262900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>709000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-665700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>461800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-143100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>286500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>149800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>874900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-214100</v>
       </c>
     </row>
